--- a/Design Files/Relay-Driver-Board-v1.0/BOM/eSpark-BOM_Relay-Driver-Board-v1.0.xlsx
+++ b/Design Files/Relay-Driver-Board-v1.0/BOM/eSpark-BOM_Relay-Driver-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="305">
   <si>
     <t>Component list</t>
   </si>
@@ -916,6 +916,24 @@
   </si>
   <si>
     <t>-----</t>
+  </si>
+  <si>
+    <t>Perpheral</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>32V Blade fuse 7.5A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t>028707.5PXCN</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t>C142688</t>
   </si>
 </sst>
 </file>
@@ -1362,17 +1380,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1390,6 +1397,17 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1679,7 +1697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -1699,6 +1717,9 @@
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1712,14 +1733,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1907,13 +1928,13 @@
       <c r="H8" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I8" s="48" t="s">
+      <c r="I8" s="45" t="s">
         <v>298</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="K8" s="45" t="s">
+      <c r="K8" s="42" t="s">
         <v>221</v>
       </c>
       <c r="L8" s="14">
@@ -1926,7 +1947,7 @@
       <c r="N8" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O8" s="47" t="s">
+      <c r="O8" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P8" s="15">
@@ -1941,7 +1962,7 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B49" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B50" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -1962,13 +1983,13 @@
       <c r="H9" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="I9" s="49" t="s">
+      <c r="I9" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J9" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="43" t="s">
         <v>222</v>
       </c>
       <c r="L9" s="20">
@@ -1981,7 +2002,7 @@
       <c r="N9" s="14">
         <v>30</v>
       </c>
-      <c r="O9" s="50" t="s">
+      <c r="O9" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P9" s="15" t="s">
@@ -2017,13 +2038,13 @@
       <c r="H10" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I10" s="49" t="s">
+      <c r="I10" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="K10" s="45" t="s">
+      <c r="K10" s="42" t="s">
         <v>223</v>
       </c>
       <c r="L10" s="14">
@@ -2036,7 +2057,7 @@
       <c r="N10" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O10" s="50" t="s">
+      <c r="O10" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P10" s="15" t="s">
@@ -2072,13 +2093,13 @@
       <c r="H11" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I11" s="49" t="s">
+      <c r="I11" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J11" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="K11" s="46" t="s">
+      <c r="K11" s="43" t="s">
         <v>224</v>
       </c>
       <c r="L11" s="20">
@@ -2091,7 +2112,7 @@
       <c r="N11" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O11" s="50" t="s">
+      <c r="O11" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P11" s="15" t="s">
@@ -2127,13 +2148,13 @@
       <c r="H12" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I12" s="49" t="s">
+      <c r="I12" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="K12" s="45" t="s">
+      <c r="K12" s="42" t="s">
         <v>225</v>
       </c>
       <c r="L12" s="14">
@@ -2146,7 +2167,7 @@
       <c r="N12" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="O12" s="50" t="s">
+      <c r="O12" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P12" s="15" t="s">
@@ -2182,13 +2203,13 @@
       <c r="H13" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="I13" s="49" t="s">
+      <c r="I13" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="K13" s="46" t="s">
+      <c r="K13" s="43" t="s">
         <v>226</v>
       </c>
       <c r="L13" s="20">
@@ -2201,7 +2222,7 @@
       <c r="N13" s="14">
         <v>20</v>
       </c>
-      <c r="O13" s="50" t="s">
+      <c r="O13" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P13" s="15" t="s">
@@ -2237,13 +2258,13 @@
       <c r="H14" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J14" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="K14" s="45" t="s">
+      <c r="K14" s="42" t="s">
         <v>225</v>
       </c>
       <c r="L14" s="14">
@@ -2256,7 +2277,7 @@
       <c r="N14" s="14">
         <v>15</v>
       </c>
-      <c r="O14" s="50" t="s">
+      <c r="O14" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P14" s="15" t="s">
@@ -2292,13 +2313,13 @@
       <c r="H15" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="I15" s="49" t="s">
+      <c r="I15" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J15" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="K15" s="46" t="s">
+      <c r="K15" s="43" t="s">
         <v>227</v>
       </c>
       <c r="L15" s="20">
@@ -2311,7 +2332,7 @@
       <c r="N15" s="14">
         <v>10</v>
       </c>
-      <c r="O15" s="50" t="s">
+      <c r="O15" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P15" s="15" t="s">
@@ -2347,13 +2368,13 @@
       <c r="H16" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I16" s="49" t="s">
+      <c r="I16" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="K16" s="45" t="s">
+      <c r="K16" s="42" t="s">
         <v>227</v>
       </c>
       <c r="L16" s="14">
@@ -2366,7 +2387,7 @@
       <c r="N16" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O16" s="50" t="s">
+      <c r="O16" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P16" s="15" t="s">
@@ -2402,13 +2423,13 @@
       <c r="H17" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I17" s="49" t="s">
+      <c r="I17" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="K17" s="46" t="s">
+      <c r="K17" s="43" t="s">
         <v>228</v>
       </c>
       <c r="L17" s="20">
@@ -2421,7 +2442,7 @@
       <c r="N17" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O17" s="50" t="s">
+      <c r="O17" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P17" s="15" t="s">
@@ -2457,13 +2478,13 @@
       <c r="H18" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="I18" s="49" t="s">
+      <c r="I18" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J18" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="45" t="s">
+      <c r="K18" s="42" t="s">
         <v>229</v>
       </c>
       <c r="L18" s="14">
@@ -2476,7 +2497,7 @@
       <c r="N18" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O18" s="50" t="s">
+      <c r="O18" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P18" s="15" t="s">
@@ -2512,13 +2533,13 @@
       <c r="H19" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="I19" s="49" t="s">
+      <c r="I19" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J19" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="K19" s="46" t="s">
+      <c r="K19" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L19" s="20">
@@ -2531,7 +2552,7 @@
       <c r="N19" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="O19" s="47" t="s">
+      <c r="O19" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P19" s="15">
@@ -2567,13 +2588,13 @@
       <c r="H20" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J20" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="K20" s="46" t="s">
+      <c r="K20" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L20" s="14">
@@ -2586,7 +2607,7 @@
       <c r="N20" s="14">
         <v>10</v>
       </c>
-      <c r="O20" s="47" t="s">
+      <c r="O20" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P20" s="21">
@@ -2622,13 +2643,13 @@
       <c r="H21" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="I21" s="49" t="s">
+      <c r="I21" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="K21" s="46" t="s">
+      <c r="K21" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L21" s="20">
@@ -2641,7 +2662,7 @@
       <c r="N21" s="14">
         <v>6</v>
       </c>
-      <c r="O21" s="47" t="s">
+      <c r="O21" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P21" s="15">
@@ -2677,13 +2698,13 @@
       <c r="H22" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I22" s="49" t="s">
+      <c r="I22" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J22" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L22" s="14">
@@ -2696,7 +2717,7 @@
       <c r="N22" s="14">
         <v>6</v>
       </c>
-      <c r="O22" s="50" t="s">
+      <c r="O22" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P22" s="15" t="s">
@@ -2732,13 +2753,13 @@
       <c r="H23" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="I23" s="49" t="s">
+      <c r="I23" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J23" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="K23" s="46" t="s">
+      <c r="K23" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L23" s="20">
@@ -2751,7 +2772,7 @@
       <c r="N23" s="14">
         <v>6</v>
       </c>
-      <c r="O23" s="47" t="s">
+      <c r="O23" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P23" s="15">
@@ -2787,13 +2808,13 @@
       <c r="H24" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="I24" s="49" t="s">
+      <c r="I24" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J24" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="K24" s="46" t="s">
+      <c r="K24" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L24" s="14">
@@ -2806,7 +2827,7 @@
       <c r="N24" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="O24" s="50" t="s">
+      <c r="O24" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P24" s="15" t="s">
@@ -2842,13 +2863,13 @@
       <c r="H25" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="I25" s="49" t="s">
+      <c r="I25" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="K25" s="46" t="s">
+      <c r="K25" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L25" s="20">
@@ -2861,7 +2882,7 @@
       <c r="N25" s="14">
         <v>10</v>
       </c>
-      <c r="O25" s="50" t="s">
+      <c r="O25" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P25" s="15" t="s">
@@ -2897,13 +2918,13 @@
       <c r="H26" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="I26" s="49" t="s">
+      <c r="I26" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J26" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="K26" s="46" t="s">
+      <c r="K26" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L26" s="14">
@@ -2916,7 +2937,7 @@
       <c r="N26" s="14">
         <v>25</v>
       </c>
-      <c r="O26" s="50" t="s">
+      <c r="O26" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P26" s="15" t="s">
@@ -2952,13 +2973,13 @@
       <c r="H27" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="I27" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="K27" s="46" t="s">
+      <c r="K27" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L27" s="20">
@@ -2971,7 +2992,7 @@
       <c r="N27" s="14">
         <v>21</v>
       </c>
-      <c r="O27" s="50" t="s">
+      <c r="O27" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P27" s="15" t="s">
@@ -3007,13 +3028,13 @@
       <c r="H28" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="I28" s="49" t="s">
+      <c r="I28" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J28" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="K28" s="45" t="s">
+      <c r="K28" s="42" t="s">
         <v>230</v>
       </c>
       <c r="L28" s="14">
@@ -3026,7 +3047,7 @@
       <c r="N28" s="14">
         <v>6</v>
       </c>
-      <c r="O28" s="50" t="s">
+      <c r="O28" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P28" s="15" t="s">
@@ -3062,13 +3083,13 @@
       <c r="H29" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="I29" s="49" t="s">
+      <c r="I29" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J29" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="K29" s="46" t="s">
+      <c r="K29" s="43" t="s">
         <v>231</v>
       </c>
       <c r="L29" s="20">
@@ -3081,7 +3102,7 @@
       <c r="N29" s="14">
         <v>6</v>
       </c>
-      <c r="O29" s="50" t="s">
+      <c r="O29" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P29" s="15" t="s">
@@ -3117,13 +3138,13 @@
       <c r="H30" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="I30" s="49" t="s">
+      <c r="I30" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="K30" s="45" t="s">
+      <c r="K30" s="42" t="s">
         <v>250</v>
       </c>
       <c r="L30" s="14">
@@ -3136,7 +3157,7 @@
       <c r="N30" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="O30" s="50" t="s">
+      <c r="O30" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P30" s="15" t="s">
@@ -3172,13 +3193,13 @@
       <c r="H31" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="I31" s="49" t="s">
+      <c r="I31" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J31" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="K31" s="45" t="s">
+      <c r="K31" s="42" t="s">
         <v>250</v>
       </c>
       <c r="L31" s="20">
@@ -3191,7 +3212,7 @@
       <c r="N31" s="14">
         <v>40</v>
       </c>
-      <c r="O31" s="47" t="s">
+      <c r="O31" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P31" s="21">
@@ -3227,13 +3248,13 @@
       <c r="H32" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="I32" s="49" t="s">
+      <c r="I32" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J32" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="K32" s="45" t="s">
+      <c r="K32" s="42" t="s">
         <v>250</v>
       </c>
       <c r="L32" s="14">
@@ -3246,7 +3267,7 @@
       <c r="N32" s="14">
         <v>10</v>
       </c>
-      <c r="O32" s="47" t="s">
+      <c r="O32" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P32" s="21">
@@ -3282,13 +3303,13 @@
       <c r="H33" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I33" s="49" t="s">
+      <c r="I33" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J33" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="K33" s="46" t="s">
+      <c r="K33" s="43" t="s">
         <v>232</v>
       </c>
       <c r="L33" s="20">
@@ -3301,7 +3322,7 @@
       <c r="N33" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O33" s="47" t="s">
+      <c r="O33" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P33" s="15">
@@ -3337,13 +3358,13 @@
       <c r="H34" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I34" s="49" t="s">
+      <c r="I34" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J34" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="K34" s="45" t="s">
+      <c r="K34" s="42" t="s">
         <v>233</v>
       </c>
       <c r="L34" s="14">
@@ -3356,7 +3377,7 @@
       <c r="N34" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="O34" s="50" t="s">
+      <c r="O34" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P34" s="21" t="s">
@@ -3392,13 +3413,13 @@
       <c r="H35" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I35" s="49" t="s">
+      <c r="I35" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J35" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="K35" s="46" t="s">
+      <c r="K35" s="43" t="s">
         <v>234</v>
       </c>
       <c r="L35" s="20">
@@ -3411,7 +3432,7 @@
       <c r="N35" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="O35" s="50" t="s">
+      <c r="O35" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P35" s="21" t="s">
@@ -3447,13 +3468,13 @@
       <c r="H36" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I36" s="49" t="s">
+      <c r="I36" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J36" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="K36" s="45" t="s">
+      <c r="K36" s="42" t="s">
         <v>235</v>
       </c>
       <c r="L36" s="14">
@@ -3466,7 +3487,7 @@
       <c r="N36" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O36" s="47" t="s">
+      <c r="O36" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P36" s="21">
@@ -3502,13 +3523,13 @@
       <c r="H37" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I37" s="49" t="s">
+      <c r="I37" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="K37" s="46" t="s">
+      <c r="K37" s="43" t="s">
         <v>236</v>
       </c>
       <c r="L37" s="20">
@@ -3521,7 +3542,7 @@
       <c r="N37" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="O37" s="50" t="s">
+      <c r="O37" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P37" s="21" t="s">
@@ -3557,13 +3578,13 @@
       <c r="H38" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I38" s="49" t="s">
+      <c r="I38" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J38" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="K38" s="45" t="s">
+      <c r="K38" s="42" t="s">
         <v>237</v>
       </c>
       <c r="L38" s="14">
@@ -3576,7 +3597,7 @@
       <c r="N38" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O38" s="47" t="s">
+      <c r="O38" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P38" s="21">
@@ -3612,13 +3633,13 @@
       <c r="H39" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I39" s="49" t="s">
+      <c r="I39" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="K39" s="46" t="s">
+      <c r="K39" s="43" t="s">
         <v>238</v>
       </c>
       <c r="L39" s="20">
@@ -3631,7 +3652,7 @@
       <c r="N39" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O39" s="50" t="s">
+      <c r="O39" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P39" s="21" t="s">
@@ -3667,13 +3688,13 @@
       <c r="H40" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I40" s="49" t="s">
+      <c r="I40" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J40" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="K40" s="45" t="s">
+      <c r="K40" s="42" t="s">
         <v>239</v>
       </c>
       <c r="L40" s="14">
@@ -3686,7 +3707,7 @@
       <c r="N40" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O40" s="47" t="s">
+      <c r="O40" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P40" s="21">
@@ -3722,13 +3743,13 @@
       <c r="H41" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I41" s="49" t="s">
+      <c r="I41" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="K41" s="46" t="s">
+      <c r="K41" s="43" t="s">
         <v>240</v>
       </c>
       <c r="L41" s="20">
@@ -3741,7 +3762,7 @@
       <c r="N41" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="O41" s="50" t="s">
+      <c r="O41" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P41" s="21" t="s">
@@ -3777,13 +3798,13 @@
       <c r="H42" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I42" s="49" t="s">
+      <c r="I42" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J42" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="K42" s="45" t="s">
+      <c r="K42" s="42" t="s">
         <v>241</v>
       </c>
       <c r="L42" s="14">
@@ -3796,7 +3817,7 @@
       <c r="N42" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O42" s="47" t="s">
+      <c r="O42" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P42" s="21">
@@ -3832,13 +3853,13 @@
       <c r="H43" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="I43" s="49" t="s">
+      <c r="I43" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="K43" s="46" t="s">
+      <c r="K43" s="43" t="s">
         <v>242</v>
       </c>
       <c r="L43" s="20">
@@ -3851,7 +3872,7 @@
       <c r="N43" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="O43" s="50" t="s">
+      <c r="O43" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P43" s="21" t="s">
@@ -3887,13 +3908,13 @@
       <c r="H44" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I44" s="49" t="s">
+      <c r="I44" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J44" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="K44" s="45" t="s">
+      <c r="K44" s="42" t="s">
         <v>243</v>
       </c>
       <c r="L44" s="14">
@@ -3906,7 +3927,7 @@
       <c r="N44" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O44" s="50" t="s">
+      <c r="O44" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P44" s="21" t="s">
@@ -3942,13 +3963,13 @@
       <c r="H45" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="I45" s="49" t="s">
+      <c r="I45" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J45" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="K45" s="46" t="s">
+      <c r="K45" s="43" t="s">
         <v>244</v>
       </c>
       <c r="L45" s="20">
@@ -3961,7 +3982,7 @@
       <c r="N45" s="14">
         <v>6</v>
       </c>
-      <c r="O45" s="50" t="s">
+      <c r="O45" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P45" s="21" t="s">
@@ -3997,13 +4018,13 @@
       <c r="H46" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I46" s="49" t="s">
+      <c r="I46" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J46" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="K46" s="45" t="s">
+      <c r="K46" s="42" t="s">
         <v>245</v>
       </c>
       <c r="L46" s="14">
@@ -4016,7 +4037,7 @@
       <c r="N46" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="O46" s="47" t="s">
+      <c r="O46" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P46" s="15">
@@ -4052,13 +4073,13 @@
       <c r="H47" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="I47" s="49" t="s">
+      <c r="I47" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J47" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="K47" s="46" t="s">
+      <c r="K47" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L47" s="20">
@@ -4071,7 +4092,7 @@
       <c r="N47" s="14">
         <v>6</v>
       </c>
-      <c r="O47" s="50" t="s">
+      <c r="O47" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P47" s="21" t="s">
@@ -4107,13 +4128,13 @@
       <c r="H48" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="I48" s="49" t="s">
+      <c r="I48" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J48" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="K48" s="46" t="s">
+      <c r="K48" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L48" s="14">
@@ -4126,7 +4147,7 @@
       <c r="N48" s="14">
         <v>6</v>
       </c>
-      <c r="O48" s="47" t="s">
+      <c r="O48" s="44" t="s">
         <v>253</v>
       </c>
       <c r="P48" s="15">
@@ -4138,10 +4159,10 @@
       </c>
       <c r="R48" s="14"/>
     </row>
-    <row r="49" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
-      <c r="B49" s="17">
-        <f t="shared" si="0"/>
+      <c r="B49" s="16">
+        <f t="shared" ref="B49:B50" si="41">ROW(B49) - ROW($B$7)</f>
         <v>42</v>
       </c>
       <c r="C49" s="23" t="s">
@@ -4162,61 +4183,91 @@
       <c r="H49" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="I49" s="49" t="s">
+      <c r="I49" s="46" t="s">
         <v>298</v>
       </c>
       <c r="J49" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="K49" s="46" t="s">
+      <c r="K49" s="43" t="s">
         <v>250</v>
       </c>
       <c r="L49" s="20">
         <v>1</v>
       </c>
       <c r="M49" s="20">
-        <f t="shared" ref="M49" si="41">L49*5</f>
+        <f t="shared" ref="M49" si="42">L49*5</f>
         <v>5</v>
       </c>
       <c r="N49" s="14">
         <v>6</v>
       </c>
-      <c r="O49" s="50" t="s">
+      <c r="O49" s="47" t="s">
         <v>253</v>
       </c>
       <c r="P49" s="15" t="s">
         <v>297</v>
       </c>
       <c r="Q49" s="21">
-        <f t="shared" ref="Q49" si="42">P49*N49</f>
+        <f t="shared" ref="Q49" si="43">P49*N49</f>
         <v>9.2712000000000003</v>
       </c>
       <c r="R49" s="20"/>
     </row>
-    <row r="50" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="18">
-        <f>SUM(Q8:Q49)</f>
-        <v>107.16929999999999</v>
-      </c>
-      <c r="R50" s="1"/>
+      <c r="B50" s="16">
+        <f t="shared" si="41"/>
+        <v>43</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="G50" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="I50" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="K50" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="L50" s="20">
+        <v>1</v>
+      </c>
+      <c r="M50" s="20">
+        <f t="shared" ref="M50" si="44">L50*5</f>
+        <v>5</v>
+      </c>
+      <c r="N50" s="14">
+        <v>5</v>
+      </c>
+      <c r="O50" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="P50" s="15">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="Q50" s="21">
+        <f t="shared" ref="Q50" si="45">P50*N50</f>
+        <v>0.38449999999999995</v>
+      </c>
+      <c r="R50" s="20"/>
     </row>
     <row r="51" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
@@ -4232,25 +4283,50 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
-      <c r="N51" s="43" t="s">
+      <c r="N51" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="O51" s="50"/>
+      <c r="P51" s="50"/>
+      <c r="Q51" s="18">
+        <f>SUM(Q8:Q50)</f>
+        <v>107.5538</v>
+      </c>
+      <c r="R51" s="1"/>
+    </row>
+    <row r="52" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="O51" s="44"/>
-      <c r="P51" s="44"/>
-      <c r="Q51" s="19">
-        <f>Q50/5</f>
-        <v>21.433859999999999</v>
-      </c>
-      <c r="R51" s="1"/>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="M63" s="38"/>
+      <c r="O52" s="50"/>
+      <c r="P52" s="50"/>
+      <c r="Q52" s="19">
+        <f>Q51/5</f>
+        <v>21.510759999999998</v>
+      </c>
+      <c r="R52" s="1"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M64" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N50:P50"/>
     <mergeCell ref="N51:P51"/>
+    <mergeCell ref="N52:P52"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O19" r:id="rId1"/>
@@ -4295,8 +4371,9 @@
     <hyperlink ref="O45" r:id="rId40"/>
     <hyperlink ref="O47" r:id="rId41"/>
     <hyperlink ref="O49" r:id="rId42"/>
+    <hyperlink ref="O50" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId43"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId44"/>
 </worksheet>
 </file>